--- a/chatbot/data.xlsx
+++ b/chatbot/data.xlsx
@@ -397,7 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:C110"/>
+  <dimension ref="A1:C112"/>
   <sheetData>
     <row r="1" xml:space="preserve">
       <c r="A1" t="str">
@@ -1895,9 +1895,31 @@
 We are located at Plot No. 10, P.C. Pawar Marg, Gangapur Rd, Anandvalli, Nashik, Maharashtra 422013. We can't wait to welcome you for some delicious Dimsums, Sushi, or perhaps our famous Watermelon Feta Fries!</v>
       </c>
     </row>
+    <row r="111">
+      <c r="A111" t="str">
+        <v>6/1/2026, 7:58:50 pm</v>
+      </c>
+      <c r="B111" t="str">
+        <v>Do you serve jain food ?</v>
+      </c>
+      <c r="C111" t="str">
+        <v>AI is currently unavailable. Please contact the hotel directly.</v>
+      </c>
+    </row>
+    <row r="112">
+      <c r="A112" t="str">
+        <v>6/1/2026, 7:59:15 pm</v>
+      </c>
+      <c r="B112" t="str">
+        <v>Do you have free wifi</v>
+      </c>
+      <c r="C112" t="str">
+        <v>AI is currently unavailable. Please contact the hotel directly.</v>
+      </c>
+    </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:C110"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:C112"/>
   </ignoredErrors>
 </worksheet>
 </file>